--- a/endpoint_excels/iss__analyticalproducts__futoi__securities__security.xlsx
+++ b/endpoint_excels/iss__analyticalproducts__futoi__securities__security.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="futoi" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="futoi.dates" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COLUMN_DOCS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,16 +30,26 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -52,14 +63,34 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -135,6 +166,43 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TBL_01_iss__analyticalpro" displayName="TBL_01_iss__analyticalpro" ref="A1:C3" headerRowCount="1">
+  <autoFilter ref="A1:C3"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="ERROR_MESSAGE"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TBL_02_iss__analyticalpro" displayName="TBL_02_iss__analyticalpro" ref="A1:D3" headerRowCount="1">
+  <autoFilter ref="A1:D3"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="from"/>
+    <tableColumn id="4" name="till"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ENDPOINT_COLUMN_DOCS" displayName="ENDPOINT_COLUMN_DOCS" ref="A1:C8" headerRowCount="1">
+  <autoFilter ref="A1:C8"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="SHEET_NAME"/>
+    <tableColumn id="2" name="COLUMN_NAME"/>
+    <tableColumn id="3" name="DESCRIPTION_RU"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,8 +496,13 @@
   </sheetPr>
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SECID</t>
@@ -447,34 +520,34 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/analyticalproducts/futoi/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Invalid date value.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/analyticalproducts/futoi/securities/RU000A1041Q0.json</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Invalid date value.</t>
         </is>
@@ -482,6 +555,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -493,58 +569,225 @@
   </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SECID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>REQUEST_URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>till</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/analyticalproducts/futoi/securities/SU26238RMFS4.json</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>RU000A1041Q0</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/analyticalproducts/futoi/securities/RU000A1041Q0.json</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>SHEET_NAME</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>COLUMN_NAME</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DESCRIPTION_RU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>futoi</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
           <t>SECID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Код финансового инструмента (ценной бумаги) в ISS MOEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>futoi</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>REQUEST_URL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>URL endpoint ISS, откуда получены данные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>futoi</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ERROR_MESSAGE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>futoi.dates</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>SECID</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Код финансового инструмента (ценной бумаги) в ISS MOEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>futoi.dates</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>REQUEST_URL</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>URL endpoint ISS, откуда получены данные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>futoi.dates</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>futoi.dates</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>till</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/analyticalproducts/futoi/securities/SU26238RMFS4.json</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RU000A1041Q0</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/analyticalproducts/futoi/securities/RU000A1041Q0.json</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/endpoint_excels/iss__analyticalproducts__futoi__securities__security.xlsx
+++ b/endpoint_excels/iss__analyticalproducts__futoi__securities__security.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,16 +29,26 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -52,14 +62,31 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -135,6 +162,31 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TBL_01_iss__analyticalpro" displayName="TBL_01_iss__analyticalpro" ref="A1:C3" headerRowCount="1">
+  <autoFilter ref="A1:C3"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="ERROR_MESSAGE"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TBL_02_iss__analyticalpro" displayName="TBL_02_iss__analyticalpro" ref="A1:D3" headerRowCount="1">
+  <autoFilter ref="A1:D3"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="from"/>
+    <tableColumn id="4" name="till"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,8 +480,13 @@
   </sheetPr>
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SECID</t>
@@ -447,34 +504,34 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/analyticalproducts/futoi/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Invalid date value.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/analyticalproducts/futoi/securities/RU000A1041Q0.json</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Invalid date value.</t>
         </is>
@@ -482,6 +539,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -493,8 +553,14 @@
   </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SECID</t>
@@ -517,34 +583,37 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/analyticalproducts/futoi/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/analyticalproducts/futoi/securities/RU000A1041Q0.json</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>